--- a/data/trans_orig/P25C_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dejó de fumar con o sin ayuda específica en 2023</t>
+          <t>Población según si dejó de fumar con o sin ayuda específica en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3071</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>43062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>35327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43704</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84681</t>
+          <t>84137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94581</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31739</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326033</t>
+          <t>327172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75745</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>83912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402497</t>
+          <t>404220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431633</t>
+          <t>432119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>37056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132054</t>
+          <t>131139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147488</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69316</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79085</t>
+          <t>79306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205899</t>
+          <t>206022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224181</t>
+          <t>224159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138035</t>
+          <t>138116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149416</t>
+          <t>149496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37052</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178792</t>
+          <t>178128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>190890</t>
+          <t>190798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102746</t>
+          <t>103665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112318</t>
+          <t>112444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119603</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129264</t>
+          <t>128901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>68636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97483</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>782085</t>
+          <t>780917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>831587</t>
+          <t>834511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299448</t>
+          <t>299904</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316454</t>
+          <t>316421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1089513</t>
+          <t>1089264</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1150053</t>
+          <t>1149535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>40437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48343</t>
+          <t>52592</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>90571</t>
+          <t>99080</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84137</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>103057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>342303</t>
+          <t>107340</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327172</t>
+          <t>101045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>112016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80610</t>
+          <t>85266</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83912</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>422913</t>
+          <t>192607</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404220</t>
+          <t>184170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>432119</t>
+          <t>198204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>347127</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434236</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>29649</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>140776</t>
+          <t>147260</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131139</t>
+          <t>137353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146979</t>
+          <t>154089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>82498</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69184</t>
+          <t>76413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>86914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>215982</t>
+          <t>229759</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>220488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224159</t>
+          <t>237857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>165082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243078</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>26558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>144583</t>
+          <t>159129</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138116</t>
+          <t>151785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>164037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>185588</t>
+          <t>202979</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178128</t>
+          <t>193642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>208360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>108930</t>
+          <t>120113</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103665</t>
+          <t>114400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112444</t>
+          <t>124223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>124925</t>
+          <t>137929</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119022</t>
+          <t>131660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128901</t>
+          <t>142509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68636</t>
+          <t>64357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>72222</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>64444</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>805868</t>
+          <t>611308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>780917</t>
+          <t>595862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>834511</t>
+          <t>622759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>308907</t>
+          <t>335291</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299904</t>
+          <t>326142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316421</t>
+          <t>343208</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>946599</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1089264</t>
+          <t>929283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1149535</t>
+          <t>961665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
